--- a/kanban_system/output/library_linked/文莱法规清单.xlsx
+++ b/kanban_system/output/library_linked/文莱法规清单.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="1" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="6160" yWindow="4470" windowWidth="14400" windowHeight="8170" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文莱" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="文莱" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>

--- a/kanban_system/output/library_linked/文莱法规清单.xlsx
+++ b/kanban_system/output/library_linked/文莱法规清单.xlsx
@@ -1075,6 +1075,11 @@
           <t>东盟成员国汽车产品型式认证互认框架；文莱为缔约方</t>
         </is>
       </c>
+      <c r="Z5" s="15" t="inlineStr">
+        <is>
+          <t>INS-2026-021 印尼车辆型式认证(VTA)体系及向UN法规靠拢路线图｜GIIAS 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
@@ -3340,6 +3345,11 @@
         </is>
       </c>
       <c r="Y28" s="10" t="n"/>
+      <c r="Z28" s="15" t="inlineStr">
+        <is>
+          <t>INS-2026-021 印尼车辆型式认证(VTA)体系及向UN法规靠拢路线图｜GIIAS 2025</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="n">
@@ -4015,6 +4025,11 @@
         </is>
       </c>
       <c r="Y35" s="10" t="n"/>
+      <c r="Z35" s="15" t="inlineStr">
+        <is>
+          <t>INS-2026-021 印尼车辆型式认证(VTA)体系及向UN法规靠拢路线图｜GIIAS 2025</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="n">
@@ -4114,7 +4129,7 @@
       <c r="Y36" s="10" t="n"/>
       <c r="Z36" s="15" t="inlineStr">
         <is>
-          <t>INS-2026-019 巴西认证为何混合联合国、美国法规？ECE、UN R、CONTRAN与RESOLUTION的区别</t>
+          <t>INS-2026-019 巴西认证为何混合联合国、美国法规？ECE、UN R、CONTRAN与RESOLUTION的区别 ; INS-2026-021 印尼车辆型式认证(VTA)体系及向UN法规靠拢路线图｜GIIAS 2025</t>
         </is>
       </c>
     </row>
